--- a/data/source/weekly/cs-en-us-100pct.xlsx
+++ b/data/source/weekly/cs-en-us-100pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -936,32 +936,32 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
+        <v>2</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>4</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="G16" s="14">
+        <v>2</v>
+      </c>
+      <c r="H16" s="15">
+        <v>50</v>
       </c>
       <c r="I16" s="14">
         <v>7</v>
       </c>
       <c r="J16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K16" s="15">
-        <v>600</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L16" s="15">
         <v>75</v>
@@ -970,7 +970,7 @@
         <v>-36.363636363636</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.419354838709</v>
+        <v>-78.787878787878</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
-      </c>
-      <c r="D17" s="14">
-        <v>1</v>
-      </c>
-      <c r="E17" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G17" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17" s="15">
-        <v>66.666666666666</v>
+        <v>200</v>
       </c>
       <c r="I17" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J17" s="14">
         <v>8</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L17" s="15">
-        <v>-38.461538461538</v>
+        <v>-37.5</v>
       </c>
       <c r="M17" s="15">
-        <v>-11.111111111111</v>
+        <v>11.111111111111</v>
       </c>
       <c r="N17" s="15">
-        <v>-50</v>
+        <v>-47.368421052631</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1021,17 +1021,17 @@
       <c r="C18" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-100</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G18" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H18" s="15">
         <v>-100</v>
@@ -1046,77 +1046,77 @@
         <v>-60</v>
       </c>
       <c r="L18" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M18" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-96</v>
+        <v>-96.721311475409</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>20</v>
+      <c r="C19" s="14">
+        <v>2</v>
       </c>
       <c r="D19" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19" s="14">
         <v>8</v>
       </c>
       <c r="H19" s="15">
+        <v>-37.5</v>
+      </c>
+      <c r="I19" s="14">
+        <v>7</v>
+      </c>
+      <c r="J19" s="14">
+        <v>11</v>
+      </c>
+      <c r="K19" s="15">
+        <v>-36.363636363636</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-63.157894736842</v>
+      </c>
+      <c r="M19" s="15">
         <v>-50</v>
       </c>
-      <c r="I19" s="14">
-        <v>5</v>
-      </c>
-      <c r="J19" s="14">
-        <v>9</v>
-      </c>
-      <c r="K19" s="15">
-        <v>-44.444444444444</v>
-      </c>
-      <c r="L19" s="15">
-        <v>-68.75</v>
-      </c>
-      <c r="M19" s="15">
-        <v>-58.333333333333</v>
-      </c>
       <c r="N19" s="15">
-        <v>-54.545454545454</v>
+        <v>-58.823529411764</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>0</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" s="14">
         <v>3</v>
@@ -1128,13 +1128,13 @@
         <v>50</v>
       </c>
       <c r="L20" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="M20" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.956521739130</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" s="17">
         <v>4</v>
       </c>
       <c r="E21" s="18">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G21" s="17">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.789473684210</v>
+        <v>0</v>
       </c>
       <c r="I21" s="17">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J21" s="17">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K21" s="18">
         <v>0</v>
       </c>
       <c r="L21" s="18">
-        <v>-36.585365853658</v>
+        <v>-38.775510204081</v>
       </c>
       <c r="M21" s="18">
-        <v>-33.333333333333</v>
+        <v>-30.232558139534</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.597014925373</v>
+        <v>-81.366459627329</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,8 +1191,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="14">
-        <v>1</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D24" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E24" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G24" s="14">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H24" s="15">
-        <v>12.5</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="I24" s="14">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="J24" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K24" s="15">
-        <v>14.285714285714</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L24" s="15">
-        <v>37.142857142857</v>
+        <v>44.736842105263</v>
       </c>
       <c r="M24" s="15">
-        <v>33.333333333333</v>
+        <v>44.736842105263</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1309,31 +1309,31 @@
         <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="F25" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G25" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H25" s="15">
-        <v>4.761904761904</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I25" s="14">
+        <v>30</v>
+      </c>
+      <c r="J25" s="14">
         <v>25</v>
       </c>
-      <c r="J25" s="14">
-        <v>24</v>
-      </c>
       <c r="K25" s="15">
-        <v>4.166666666666</v>
+        <v>20</v>
       </c>
       <c r="L25" s="15">
-        <v>47.058823529411</v>
+        <v>76.470588235294</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1346,38 +1346,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="14">
-        <v>2</v>
+      <c r="C26" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D26" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E26" s="15">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F26" s="14">
+        <v>8</v>
+      </c>
+      <c r="G26" s="14">
         <v>10</v>
       </c>
-      <c r="G26" s="14">
-        <v>18</v>
-      </c>
       <c r="H26" s="15">
-        <v>-44.444444444444</v>
+        <v>-20</v>
       </c>
       <c r="I26" s="14">
         <v>15</v>
       </c>
       <c r="J26" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K26" s="15">
-        <v>-25</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L26" s="15">
-        <v>-25</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="M26" s="15">
-        <v>-46.428571428571</v>
+        <v>-55.882352941176</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1496,8 +1496,8 @@
       <c r="K29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
+      <c r="L29" s="15">
+        <v>-100</v>
       </c>
       <c r="M29" s="15">
         <v>-100</v>
@@ -1537,8 +1537,8 @@
       <c r="K30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
+      <c r="L30" s="15">
+        <v>-100</v>
       </c>
       <c r="M30" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-100pct.xlsx
+++ b/data/source/weekly/cs-en-us-100pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -888,7 +888,7 @@
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -907,11 +907,11 @@
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>-100</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>20</v>
@@ -940,37 +940,37 @@
         <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
         <v>-100</v>
       </c>
       <c r="F16" s="14">
+        <v>1</v>
+      </c>
+      <c r="G16" s="14">
         <v>3</v>
       </c>
-      <c r="G16" s="14">
-        <v>2</v>
-      </c>
       <c r="H16" s="15">
-        <v>50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I16" s="14">
         <v>7</v>
       </c>
       <c r="J16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K16" s="15">
-        <v>133.333333333333</v>
+        <v>75</v>
       </c>
       <c r="L16" s="15">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="M16" s="15">
         <v>-36.363636363636</v>
       </c>
       <c r="N16" s="15">
-        <v>-78.787878787878</v>
+        <v>-82.051282051282</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,48 +978,48 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D17" s="14">
+        <v>1</v>
+      </c>
+      <c r="E17" s="15">
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G17" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" s="15">
-        <v>200</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J17" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K17" s="15">
-        <v>25</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L17" s="15">
-        <v>-37.5</v>
+        <v>-45</v>
       </c>
       <c r="M17" s="15">
-        <v>11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="N17" s="15">
-        <v>-47.368421052631</v>
+        <v>-47.619047619047</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>20</v>
@@ -1027,32 +1027,32 @@
       <c r="E18" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="13" t="s">
-        <v>20</v>
+      <c r="F18" s="14">
+        <v>1</v>
       </c>
       <c r="G18" s="14">
         <v>3</v>
       </c>
       <c r="H18" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" s="14">
         <v>5</v>
       </c>
       <c r="K18" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="L18" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="M18" s="15">
-        <v>-66.666666666666</v>
+        <v>-62.5</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.721311475409</v>
+        <v>-95.890410958904</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,48 +1060,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" s="14">
         <v>2</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F19" s="14">
         <v>5</v>
       </c>
       <c r="G19" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H19" s="15">
-        <v>-37.5</v>
+        <v>-50</v>
       </c>
       <c r="I19" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J19" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K19" s="15">
-        <v>-36.363636363636</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="L19" s="15">
-        <v>-63.157894736842</v>
+        <v>-52.380952380952</v>
       </c>
       <c r="M19" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N19" s="15">
-        <v>-58.823529411764</v>
+        <v>-44.444444444444</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>2</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1110,31 +1110,31 @@
         <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
         <v>1</v>
       </c>
       <c r="H20" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I20" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J20" s="14">
         <v>2</v>
       </c>
       <c r="K20" s="15">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="L20" s="15">
-        <v>-50</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="M20" s="15">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.888888888888</v>
+        <v>-82.142857142857</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D21" s="17">
         <v>4</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F21" s="17">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G21" s="17">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H21" s="18">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I21" s="17">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="J21" s="17">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K21" s="18">
-        <v>0</v>
+        <v>8.823529411764</v>
       </c>
       <c r="L21" s="18">
-        <v>-38.775510204081</v>
+        <v>-42.1875</v>
       </c>
       <c r="M21" s="18">
-        <v>-30.232558139534</v>
+        <v>-22.916666666666</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.366459627329</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>9</v>
+      </c>
+      <c r="D24" s="14">
         <v>7</v>
       </c>
-      <c r="D24" s="14">
-        <v>3</v>
-      </c>
       <c r="E24" s="15">
-        <v>133.333333333333</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F24" s="14">
+        <v>30</v>
+      </c>
+      <c r="G24" s="14">
         <v>27</v>
       </c>
-      <c r="G24" s="14">
-        <v>29</v>
-      </c>
       <c r="H24" s="15">
-        <v>-6.896551724137</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I24" s="14">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="J24" s="14">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="K24" s="15">
-        <v>22.222222222222</v>
+        <v>23.076923076923</v>
       </c>
       <c r="L24" s="15">
-        <v>44.736842105263</v>
+        <v>28</v>
       </c>
       <c r="M24" s="15">
-        <v>44.736842105263</v>
+        <v>48.837209302325</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G25" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H25" s="15">
-        <v>11.111111111111</v>
+        <v>26.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J25" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K25" s="15">
-        <v>20</v>
+        <v>17.857142857142</v>
       </c>
       <c r="L25" s="15">
-        <v>76.470588235294</v>
+        <v>50</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1346,38 +1346,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>20</v>
+      <c r="C26" s="14">
+        <v>1</v>
       </c>
       <c r="D26" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G26" s="14">
         <v>10</v>
       </c>
       <c r="H26" s="15">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="I26" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J26" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K26" s="15">
-        <v>-28.571428571428</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="L26" s="15">
-        <v>-34.782608695652</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M26" s="15">
-        <v>-55.882352941176</v>
+        <v>-56.756756756756</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1399,11 +1399,11 @@
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <v>-100</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="13" t="s">
         <v>20</v>
@@ -1440,11 +1440,11 @@
       <c r="F28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G28" s="14">
-        <v>1</v>
-      </c>
-      <c r="H28" s="15">
-        <v>-100</v>
+      <c r="G28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I28" s="14">
         <v>1</v>
@@ -1628,8 +1628,8 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-100pct.xlsx
+++ b/data/source/weekly/cs-en-us-100pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -863,8 +863,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -936,41 +936,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="14">
+      <c r="C16" s="14">
         <v>1</v>
       </c>
-      <c r="E16" s="15">
-        <v>-100</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="14">
         <v>3</v>
       </c>
       <c r="H16" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J16" s="14">
         <v>4</v>
       </c>
       <c r="K16" s="15">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="L16" s="15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M16" s="15">
-        <v>-36.363636363636</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.051282051282</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -981,78 +981,78 @@
         <v>1</v>
       </c>
       <c r="D17" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="14">
+        <v>5</v>
+      </c>
+      <c r="G17" s="14">
         <v>4</v>
       </c>
-      <c r="G17" s="14">
-        <v>3</v>
-      </c>
       <c r="H17" s="15">
-        <v>33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="I17" s="14">
+        <v>13</v>
+      </c>
+      <c r="J17" s="14">
         <v>11</v>
       </c>
-      <c r="J17" s="14">
-        <v>9</v>
-      </c>
       <c r="K17" s="15">
-        <v>22.222222222222</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L17" s="15">
-        <v>-45</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="M17" s="15">
-        <v>0</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="N17" s="15">
-        <v>-47.619047619047</v>
+        <v>-40.909090909090</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="E18" s="15">
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
         <v>1</v>
       </c>
       <c r="G18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I18" s="14">
         <v>3</v>
       </c>
       <c r="J18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K18" s="15">
+        <v>-50</v>
+      </c>
+      <c r="L18" s="15">
         <v>-40</v>
       </c>
-      <c r="L18" s="15">
-        <v>-25</v>
-      </c>
       <c r="M18" s="15">
-        <v>-62.5</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.890410958904</v>
+        <v>-96.296296296296</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1063,45 +1063,45 @@
         <v>3</v>
       </c>
       <c r="D19" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" s="15">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F19" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G19" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H19" s="15">
-        <v>-50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J19" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K19" s="15">
-        <v>-23.076923076923</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L19" s="15">
-        <v>-52.380952380952</v>
+        <v>-48</v>
       </c>
       <c r="M19" s="15">
-        <v>-33.333333333333</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="N19" s="15">
-        <v>-44.444444444444</v>
+        <v>-27.777777777777</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>2</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1128,13 +1128,13 @@
         <v>150</v>
       </c>
       <c r="L20" s="15">
-        <v>-64.285714285714</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-82.142857142857</v>
+        <v>-85.294117647058</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D21" s="17">
         <v>4</v>
       </c>
       <c r="E21" s="18">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="F21" s="17">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G21" s="17">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H21" s="18">
-        <v>-25</v>
+        <v>18.75</v>
       </c>
       <c r="I21" s="17">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J21" s="17">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K21" s="18">
-        <v>8.823529411764</v>
+        <v>13.157894736842</v>
       </c>
       <c r="L21" s="18">
-        <v>-42.1875</v>
+        <v>-42.666666666666</v>
       </c>
       <c r="M21" s="18">
-        <v>-22.916666666666</v>
+        <v>-27.118644067796</v>
       </c>
       <c r="N21" s="18">
-        <v>-80</v>
+        <v>-78.606965174129</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1209,11 +1209,11 @@
       <c r="K22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L22" s="13" t="s">
-        <v>21</v>
+      <c r="L22" s="15">
+        <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1226,26 +1226,26 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
+      <c r="G23" s="14">
+        <v>1</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-100</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>20</v>
       </c>
       <c r="J23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" s="15">
         <v>-100</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D24" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E24" s="15">
-        <v>28.571428571428</v>
+        <v>-37.5</v>
       </c>
       <c r="F24" s="14">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G24" s="14">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H24" s="15">
-        <v>11.111111111111</v>
+        <v>31.818181818181</v>
       </c>
       <c r="I24" s="14">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J24" s="14">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="K24" s="15">
-        <v>23.076923076923</v>
+        <v>15</v>
       </c>
       <c r="L24" s="15">
-        <v>28</v>
+        <v>13.114754098360</v>
       </c>
       <c r="M24" s="15">
-        <v>48.837209302325</v>
+        <v>53.333333333333</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" s="14">
         <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G25" s="14">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H25" s="15">
-        <v>26.666666666666</v>
+        <v>55.555555555555</v>
       </c>
       <c r="I25" s="14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J25" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K25" s="15">
-        <v>17.857142857142</v>
+        <v>9.677419354838</v>
       </c>
       <c r="L25" s="15">
-        <v>50</v>
+        <v>25.925925925925</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
         <v>6</v>
       </c>
       <c r="G26" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H26" s="15">
-        <v>-40</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J26" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K26" s="15">
-        <v>-30.434782608695</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="L26" s="15">
-        <v>-42.857142857142</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="M26" s="15">
-        <v>-56.756756756756</v>
+        <v>-59.090909090909</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1431,29 +1431,29 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>21</v>
+      <c r="G28" s="14">
+        <v>1</v>
+      </c>
+      <c r="H28" s="15">
+        <v>-100</v>
       </c>
       <c r="I28" s="14">
         <v>1</v>
       </c>
       <c r="J28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L28" s="15">
         <v>-80</v>

--- a/data/source/weekly/cs-en-us-100pct.xlsx
+++ b/data/source/weekly/cs-en-us-100pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -888,7 +888,7 @@
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -939,38 +939,38 @@
       <c r="C16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="D16" s="14">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>0</v>
       </c>
       <c r="F16" s="14">
         <v>2</v>
       </c>
       <c r="G16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K16" s="15">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L16" s="15">
         <v>0</v>
       </c>
       <c r="M16" s="15">
-        <v>-38.461538461538</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="N16" s="15">
-        <v>-80</v>
+        <v>-80.851063829787</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -981,37 +981,37 @@
         <v>1</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="14">
         <v>5</v>
       </c>
       <c r="G17" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H17" s="15">
-        <v>25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J17" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K17" s="15">
-        <v>18.181818181818</v>
+        <v>0</v>
       </c>
       <c r="L17" s="15">
-        <v>-40.909090909090</v>
+        <v>-54.838709677419</v>
       </c>
       <c r="M17" s="15">
-        <v>-7.142857142857</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="N17" s="15">
-        <v>-40.909090909090</v>
+        <v>-54.838709677419</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1021,20 +1021,20 @@
       <c r="C18" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-100</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
         <v>1</v>
       </c>
       <c r="G18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
         <v>3</v>
@@ -1052,7 +1052,7 @@
         <v>-72.727272727272</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.296296296296</v>
+        <v>-96.808510638297</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,54 +1060,54 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G19" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H19" s="15">
-        <v>33.333333333333</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I19" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J19" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K19" s="15">
-        <v>-7.142857142857</v>
+        <v>-6.25</v>
       </c>
       <c r="L19" s="15">
-        <v>-48</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M19" s="15">
-        <v>-23.529411764705</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N19" s="15">
-        <v>-27.777777777777</v>
+        <v>-34.782608695652</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
       </c>
       <c r="F20" s="14">
         <v>3</v>
@@ -1119,22 +1119,22 @@
         <v>200</v>
       </c>
       <c r="I20" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="L20" s="15">
-        <v>-66.666666666666</v>
+        <v>-60</v>
       </c>
       <c r="M20" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.294117647058</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1145,45 +1145,45 @@
         <v>5</v>
       </c>
       <c r="D21" s="17">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E21" s="18">
-        <v>25</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F21" s="17">
+        <v>21</v>
+      </c>
+      <c r="G21" s="17">
         <v>19</v>
       </c>
-      <c r="G21" s="17">
-        <v>16</v>
-      </c>
       <c r="H21" s="18">
-        <v>18.75</v>
+        <v>10.526315789473</v>
       </c>
       <c r="I21" s="17">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J21" s="17">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="K21" s="18">
-        <v>13.157894736842</v>
+        <v>6.666666666666</v>
       </c>
       <c r="L21" s="18">
-        <v>-42.666666666666</v>
+        <v>-44.827586206896</v>
       </c>
       <c r="M21" s="18">
-        <v>-27.118644067796</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.606965174129</v>
+        <v>-79.831932773109</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1191,8 +1191,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1201,7 +1201,7 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>20</v>
@@ -1210,10 +1210,10 @@
         <v>21</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1226,35 +1226,35 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="14">
         <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>20</v>
       </c>
       <c r="G23" s="14">
         <v>1</v>
       </c>
       <c r="H23" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I23" s="14">
+        <v>1</v>
       </c>
       <c r="J23" s="14">
         <v>3</v>
       </c>
       <c r="K23" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L23" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="M23" s="15">
-        <v>-100</v>
+        <v>-87.5</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E24" s="15">
-        <v>-37.5</v>
+        <v>50</v>
       </c>
       <c r="F24" s="14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G24" s="14">
         <v>22</v>
       </c>
       <c r="H24" s="15">
-        <v>31.818181818181</v>
+        <v>22.727272727272</v>
       </c>
       <c r="I24" s="14">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="J24" s="14">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K24" s="15">
-        <v>15</v>
+        <v>17.1875</v>
       </c>
       <c r="L24" s="15">
-        <v>13.114754098360</v>
+        <v>5.633802816901</v>
       </c>
       <c r="M24" s="15">
-        <v>53.333333333333</v>
+        <v>53.061224489795</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
-      </c>
-      <c r="D25" s="14">
-        <v>3</v>
-      </c>
-      <c r="E25" s="15">
-        <v>-66.666666666666</v>
+        <v>2</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F25" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G25" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H25" s="15">
-        <v>55.555555555555</v>
+        <v>57.142857142857</v>
       </c>
       <c r="I25" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J25" s="14">
         <v>31</v>
       </c>
       <c r="K25" s="15">
-        <v>9.677419354838</v>
+        <v>16.129032258064</v>
       </c>
       <c r="L25" s="15">
-        <v>25.925925925925</v>
+        <v>20</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1350,34 +1350,34 @@
         <v>3</v>
       </c>
       <c r="D26" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F26" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G26" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H26" s="15">
-        <v>-33.333333333333</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="I26" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J26" s="14">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K26" s="15">
-        <v>-30.769230769230</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="L26" s="15">
-        <v>-47.058823529411</v>
+        <v>-44.736842105263</v>
       </c>
       <c r="M26" s="15">
-        <v>-59.090909090909</v>
+        <v>-59.615384615384</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1431,11 +1431,11 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-100pct.xlsx
+++ b/data/source/weekly/cs-en-us-100pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -936,23 +936,23 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
-      <c r="E16" s="15">
-        <v>0</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
         <v>2</v>
       </c>
       <c r="G16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H16" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
         <v>9</v>
@@ -970,7 +970,7 @@
         <v>-30.769230769230</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.851063829787</v>
+        <v>-83.636363636363</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
-      </c>
-      <c r="D17" s="14">
-        <v>3</v>
-      </c>
-      <c r="E17" s="15">
-        <v>-66.666666666666</v>
+        <v>4</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G17" s="14">
         <v>6</v>
       </c>
       <c r="H17" s="15">
-        <v>-16.666666666666</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J17" s="14">
         <v>14</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L17" s="15">
-        <v>-54.838709677419</v>
+        <v>-41.935483870967</v>
       </c>
       <c r="M17" s="15">
-        <v>-6.666666666666</v>
+        <v>20</v>
       </c>
       <c r="N17" s="15">
-        <v>-54.838709677419</v>
+        <v>-51.351351351351</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
+        <v>3</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K18" s="15">
+        <v>-55.555555555555</v>
+      </c>
+      <c r="L18" s="15">
         <v>-50</v>
       </c>
-      <c r="L18" s="15">
-        <v>-40</v>
-      </c>
       <c r="M18" s="15">
-        <v>-72.727272727272</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.808510638297</v>
+        <v>-96.153846153846</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
+        <v>-75</v>
+      </c>
+      <c r="F19" s="14">
+        <v>9</v>
+      </c>
+      <c r="G19" s="14">
+        <v>9</v>
+      </c>
+      <c r="H19" s="15">
         <v>0</v>
       </c>
-      <c r="F19" s="14">
-        <v>10</v>
-      </c>
-      <c r="G19" s="14">
-        <v>7</v>
-      </c>
-      <c r="H19" s="15">
-        <v>42.857142857142</v>
-      </c>
       <c r="I19" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J19" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K19" s="15">
-        <v>-6.25</v>
+        <v>-20</v>
       </c>
       <c r="L19" s="15">
-        <v>-44.444444444444</v>
+        <v>-44.827586206896</v>
       </c>
       <c r="M19" s="15">
-        <v>-16.666666666666</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="N19" s="15">
-        <v>-34.782608695652</v>
+        <v>-40.740740740740</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1110,31 +1110,31 @@
         <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" s="15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="L20" s="15">
-        <v>-60</v>
+        <v>-56.25</v>
       </c>
       <c r="M20" s="15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N20" s="15">
-        <v>-83.333333333333</v>
+        <v>-84.444444444444</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,48 +1142,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D21" s="17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E21" s="18">
-        <v>-28.571428571428</v>
+        <v>-12.5</v>
       </c>
       <c r="F21" s="17">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G21" s="17">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H21" s="18">
-        <v>10.526315789473</v>
+        <v>4.347826086956</v>
       </c>
       <c r="I21" s="17">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="J21" s="17">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K21" s="18">
-        <v>6.666666666666</v>
+        <v>3.773584905660</v>
       </c>
       <c r="L21" s="18">
-        <v>-44.827586206896</v>
+        <v>-40.860215053763</v>
       </c>
       <c r="M21" s="18">
-        <v>-22.580645161290</v>
+        <v>-14.0625</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.831932773109</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D24" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E24" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G24" s="14">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H24" s="15">
-        <v>22.727272727272</v>
+        <v>3.448275862068</v>
       </c>
       <c r="I24" s="14">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J24" s="14">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="K24" s="15">
-        <v>17.1875</v>
+        <v>14.864864864864</v>
       </c>
       <c r="L24" s="15">
-        <v>5.633802816901</v>
+        <v>1.190476190476</v>
       </c>
       <c r="M24" s="15">
-        <v>53.061224489795</v>
+        <v>49.122807017543</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1308,32 +1308,32 @@
       <c r="C25" s="14">
         <v>2</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>21</v>
+      <c r="D25" s="14">
+        <v>5</v>
+      </c>
+      <c r="E25" s="15">
+        <v>-60</v>
       </c>
       <c r="F25" s="14">
+        <v>8</v>
+      </c>
+      <c r="G25" s="14">
         <v>11</v>
       </c>
-      <c r="G25" s="14">
-        <v>7</v>
-      </c>
       <c r="H25" s="15">
-        <v>57.142857142857</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I25" s="14">
+        <v>38</v>
+      </c>
+      <c r="J25" s="14">
         <v>36</v>
       </c>
-      <c r="J25" s="14">
-        <v>31</v>
-      </c>
       <c r="K25" s="15">
-        <v>16.129032258064</v>
+        <v>5.555555555555</v>
       </c>
       <c r="L25" s="15">
-        <v>20</v>
+        <v>8.571428571428</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>3</v>
-      </c>
-      <c r="D26" s="14">
-        <v>7</v>
-      </c>
-      <c r="E26" s="15">
-        <v>-57.142857142857</v>
+        <v>5</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F26" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G26" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H26" s="15">
-        <v>-46.153846153846</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J26" s="14">
         <v>33</v>
       </c>
       <c r="K26" s="15">
-        <v>-36.363636363636</v>
+        <v>-21.212121212121</v>
       </c>
       <c r="L26" s="15">
-        <v>-44.736842105263</v>
+        <v>-36.585365853658</v>
       </c>
       <c r="M26" s="15">
-        <v>-59.615384615384</v>
+        <v>-55.172413793103</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1469,8 +1469,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1478,8 +1478,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1487,8 +1487,8 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="14">
+        <v>1</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1497,21 +1497,21 @@
         <v>21</v>
       </c>
       <c r="L29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="N29" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1519,8 +1519,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1528,8 +1528,8 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1538,13 +1538,13 @@
         <v>21</v>
       </c>
       <c r="L30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-100pct.xlsx
+++ b/data/source/weekly/cs-en-us-100pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -698,7 +698,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -949,10 +949,10 @@
         <v>2</v>
       </c>
       <c r="G16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I16" s="14">
         <v>9</v>
@@ -970,7 +970,7 @@
         <v>-30.769230769230</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.636363636363</v>
+        <v>-84.482758620689</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -987,54 +987,54 @@
         <v>21</v>
       </c>
       <c r="F17" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G17" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H17" s="15">
-        <v>16.666666666666</v>
+        <v>100</v>
       </c>
       <c r="I17" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J17" s="14">
         <v>14</v>
       </c>
       <c r="K17" s="15">
-        <v>28.571428571428</v>
+        <v>57.142857142857</v>
       </c>
       <c r="L17" s="15">
-        <v>-41.935483870967</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="M17" s="15">
-        <v>20</v>
+        <v>29.411764705882</v>
       </c>
       <c r="N17" s="15">
-        <v>-51.351351351351</v>
+        <v>-52.173913043478</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="14">
         <v>1</v>
-      </c>
-      <c r="D18" s="14">
-        <v>3</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F18" s="14">
-        <v>2</v>
       </c>
       <c r="G18" s="14">
         <v>4</v>
       </c>
       <c r="H18" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="I18" s="14">
         <v>4</v>
@@ -1046,13 +1046,13 @@
         <v>-55.555555555555</v>
       </c>
       <c r="L18" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="M18" s="15">
-        <v>-63.636363636363</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.153846153846</v>
+        <v>-96.694214876033</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,81 +1060,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E19" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G19" s="14">
         <v>9</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I19" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J19" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K19" s="15">
-        <v>-20</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L19" s="15">
-        <v>-44.827586206896</v>
+        <v>-41.935483870967</v>
       </c>
       <c r="M19" s="15">
-        <v>-15.789473684210</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="N19" s="15">
-        <v>-40.740740740740</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="14">
         <v>7</v>
       </c>
       <c r="J20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K20" s="15">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="L20" s="15">
-        <v>-56.25</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="M20" s="15">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="N20" s="15">
-        <v>-84.444444444444</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D21" s="17">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E21" s="18">
-        <v>-12.5</v>
+        <v>100</v>
       </c>
       <c r="F21" s="17">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G21" s="17">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H21" s="18">
-        <v>4.347826086956</v>
+        <v>4.545454545454</v>
       </c>
       <c r="I21" s="17">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="J21" s="17">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K21" s="18">
-        <v>3.773584905660</v>
+        <v>8.928571428571</v>
       </c>
       <c r="L21" s="18">
-        <v>-40.860215053763</v>
+        <v>-40.196078431372</v>
       </c>
       <c r="M21" s="18">
-        <v>-14.0625</v>
+        <v>-16.438356164383</v>
       </c>
       <c r="N21" s="18">
-        <v>-80</v>
+        <v>-80.817610062893</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1213,7 +1213,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>-33.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,8 +1223,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1233,28 +1233,28 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="14">
         <v>1</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" s="14">
         <v>3</v>
       </c>
       <c r="K23" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L23" s="15">
+        <v>-60</v>
+      </c>
+      <c r="M23" s="15">
         <v>-75</v>
-      </c>
-      <c r="M23" s="15">
-        <v>-87.5</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,10 +1265,10 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E24" s="15">
         <v>0</v>
@@ -1277,25 +1277,25 @@
         <v>30</v>
       </c>
       <c r="G24" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H24" s="15">
-        <v>3.448275862068</v>
+        <v>-3.225806451612</v>
       </c>
       <c r="I24" s="14">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="J24" s="14">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="K24" s="15">
-        <v>14.864864864864</v>
+        <v>13.253012048192</v>
       </c>
       <c r="L24" s="15">
-        <v>1.190476190476</v>
+        <v>-1.052631578947</v>
       </c>
       <c r="M24" s="15">
-        <v>49.122807017543</v>
+        <v>56.666666666666</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
         <v>8</v>
       </c>
       <c r="G25" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H25" s="15">
-        <v>-27.272727272727</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I25" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J25" s="14">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="K25" s="15">
-        <v>5.555555555555</v>
+        <v>-2.380952380952</v>
       </c>
       <c r="L25" s="15">
-        <v>8.571428571428</v>
+        <v>7.894736842105</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>21</v>
+        <v>6</v>
+      </c>
+      <c r="D26" s="14">
+        <v>4</v>
+      </c>
+      <c r="E26" s="15">
+        <v>50</v>
       </c>
       <c r="F26" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G26" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H26" s="15">
-        <v>0</v>
+        <v>21.428571428571</v>
       </c>
       <c r="I26" s="14">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J26" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K26" s="15">
-        <v>-21.212121212121</v>
+        <v>-13.513513513513</v>
       </c>
       <c r="L26" s="15">
-        <v>-36.585365853658</v>
+        <v>-36</v>
       </c>
       <c r="M26" s="15">
-        <v>-55.172413793103</v>
+        <v>-47.540983606557</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1431,32 +1431,32 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>20</v>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F28" s="14">
+        <v>1</v>
       </c>
       <c r="G28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K28" s="15">
         <v>-50</v>
       </c>
       <c r="L28" s="15">
-        <v>-80</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,8 +1469,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1497,7 +1497,7 @@
         <v>21</v>
       </c>
       <c r="L29" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M29" s="15">
         <v>-50</v>
@@ -1510,8 +1510,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1538,7 +1538,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
         <v>-50</v>
@@ -1637,8 +1637,8 @@
       <c r="K33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="15">
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-100pct.xlsx
+++ b/data/source/weekly/cs-en-us-100pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -698,7 +698,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -922,8 +922,8 @@
       <c r="K15" s="15">
         <v>-100</v>
       </c>
-      <c r="L15" s="13" t="s">
-        <v>21</v>
+      <c r="L15" s="15">
+        <v>-100</v>
       </c>
       <c r="M15" s="15">
         <v>-100</v>
@@ -939,29 +939,29 @@
       <c r="C16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="D16" s="14">
+        <v>3</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H16" s="15">
-        <v>100</v>
+        <v>-75</v>
       </c>
       <c r="I16" s="14">
         <v>9</v>
       </c>
       <c r="J16" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K16" s="15">
-        <v>80</v>
+        <v>12.5</v>
       </c>
       <c r="L16" s="15">
         <v>0</v>
@@ -970,7 +970,7 @@
         <v>-30.769230769230</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.482758620689</v>
+        <v>-85.245901639344</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -987,31 +987,31 @@
         <v>21</v>
       </c>
       <c r="F17" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G17" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H17" s="15">
-        <v>100</v>
+        <v>333.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J17" s="14">
         <v>14</v>
       </c>
       <c r="K17" s="15">
-        <v>57.142857142857</v>
+        <v>85.714285714285</v>
       </c>
       <c r="L17" s="15">
-        <v>-35.294117647058</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="M17" s="15">
-        <v>29.411764705882</v>
+        <v>44.444444444444</v>
       </c>
       <c r="N17" s="15">
-        <v>-52.173913043478</v>
+        <v>-50.943396226415</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1021,11 +1021,11 @@
       <c r="C18" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
         <v>1</v>
@@ -1040,19 +1040,19 @@
         <v>4</v>
       </c>
       <c r="J18" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K18" s="15">
-        <v>-55.555555555555</v>
+        <v>-60</v>
       </c>
       <c r="L18" s="15">
-        <v>-60</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="M18" s="15">
         <v>-69.230769230769</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.694214876033</v>
+        <v>-96.992481203007</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,78 +1060,78 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="14">
         <v>2</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G19" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H19" s="15">
-        <v>-11.111111111111</v>
+        <v>-40</v>
       </c>
       <c r="I19" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J19" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K19" s="15">
-        <v>-18.181818181818</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="L19" s="15">
-        <v>-41.935483870967</v>
+        <v>-44.117647058823</v>
       </c>
       <c r="M19" s="15">
-        <v>-21.739130434782</v>
+        <v>-24</v>
       </c>
       <c r="N19" s="15">
-        <v>-40</v>
+        <v>-36.666666666666</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="14">
+      <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
         <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J20" s="14">
         <v>5</v>
       </c>
       <c r="K20" s="15">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="L20" s="15">
-        <v>-61.111111111111</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M20" s="15">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="N20" s="15">
         <v>-87.5</v>
@@ -1145,37 +1145,37 @@
         <v>6</v>
       </c>
       <c r="D21" s="17">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E21" s="18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G21" s="17">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H21" s="18">
-        <v>4.545454545454</v>
+        <v>0</v>
       </c>
       <c r="I21" s="17">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="J21" s="17">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K21" s="18">
-        <v>8.928571428571</v>
+        <v>8.064516129032</v>
       </c>
       <c r="L21" s="18">
-        <v>-40.196078431372</v>
+        <v>-41.739130434782</v>
       </c>
       <c r="M21" s="18">
-        <v>-16.438356164383</v>
+        <v>-11.842105263157</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.817610062893</v>
+        <v>-80.747126436781</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1185,32 +1185,32 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>2</v>
       </c>
-      <c r="J22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>21</v>
+      <c r="J22" s="14">
+        <v>1</v>
+      </c>
+      <c r="K22" s="15">
+        <v>100</v>
       </c>
       <c r="L22" s="15">
-        <v>-33.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="M22" s="15">
         <v>-60</v>
@@ -1223,23 +1223,23 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="14">
-        <v>2</v>
-      </c>
-      <c r="G23" s="14">
-        <v>1</v>
-      </c>
-      <c r="H23" s="15">
-        <v>100</v>
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I23" s="14">
         <v>2</v>
@@ -1251,10 +1251,10 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L23" s="15">
-        <v>-60</v>
+        <v>-80</v>
       </c>
       <c r="M23" s="15">
-        <v>-75</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D24" s="14">
         <v>9</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G24" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H24" s="15">
-        <v>-3.225806451612</v>
+        <v>15.625</v>
       </c>
       <c r="I24" s="14">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="J24" s="14">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K24" s="15">
-        <v>13.253012048192</v>
+        <v>15.217391304347</v>
       </c>
       <c r="L24" s="15">
-        <v>-1.052631578947</v>
+        <v>-0.934579439252</v>
       </c>
       <c r="M24" s="15">
-        <v>56.666666666666</v>
+        <v>65.625</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F25" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G25" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H25" s="15">
-        <v>-42.857142857142</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="I25" s="14">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J25" s="14">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="K25" s="15">
-        <v>-2.380952380952</v>
+        <v>-4.081632653061</v>
       </c>
       <c r="L25" s="15">
-        <v>7.894736842105</v>
+        <v>9.302325581395</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D26" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E26" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G26" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H26" s="15">
-        <v>21.428571428571</v>
+        <v>23.076923076923</v>
       </c>
       <c r="I26" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J26" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K26" s="15">
-        <v>-13.513513513513</v>
+        <v>-12.820512820512</v>
       </c>
       <c r="L26" s="15">
-        <v>-36</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="M26" s="15">
-        <v>-47.540983606557</v>
+        <v>-50</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1414,8 +1414,8 @@
       <c r="K27" s="15">
         <v>-100</v>
       </c>
-      <c r="L27" s="13" t="s">
-        <v>21</v>
+      <c r="L27" s="15">
+        <v>-100</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1431,20 +1431,20 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>1</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="14">
         <v>2</v>
@@ -1503,7 +1503,7 @@
         <v>-50</v>
       </c>
       <c r="N29" s="15">
-        <v>-50</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1544,7 +1544,7 @@
         <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-100pct.xlsx
+++ b/data/source/weekly/cs-en-us-100pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -884,11 +884,11 @@
       <c r="L14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="15">
+        <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -936,41 +936,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="14">
+      <c r="C16" s="14">
+        <v>2</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="14">
+        <v>2</v>
+      </c>
+      <c r="G16" s="14">
         <v>3</v>
       </c>
-      <c r="E16" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F16" s="14">
-        <v>1</v>
-      </c>
-      <c r="G16" s="14">
-        <v>4</v>
-      </c>
       <c r="H16" s="15">
-        <v>-75</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J16" s="14">
         <v>8</v>
       </c>
       <c r="K16" s="15">
-        <v>12.5</v>
+        <v>37.5</v>
       </c>
       <c r="L16" s="15">
-        <v>0</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-30.769230769230</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.245901639344</v>
+        <v>-82.258064516129</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D17" s="14">
+        <v>3</v>
+      </c>
+      <c r="E17" s="15">
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" s="14">
         <v>3</v>
       </c>
       <c r="H17" s="15">
-        <v>333.333333333333</v>
+        <v>366.666666666667</v>
       </c>
       <c r="I17" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J17" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K17" s="15">
-        <v>85.714285714285</v>
+        <v>64.705882352941</v>
       </c>
       <c r="L17" s="15">
-        <v>-38.095238095238</v>
+        <v>-40.425531914893</v>
       </c>
       <c r="M17" s="15">
-        <v>44.444444444444</v>
+        <v>55.555555555555</v>
       </c>
       <c r="N17" s="15">
-        <v>-50.943396226415</v>
+        <v>-50.877192982456</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1021,11 +1021,11 @@
       <c r="C18" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-100</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
         <v>1</v>
@@ -1046,13 +1046,13 @@
         <v>-60</v>
       </c>
       <c r="L18" s="15">
-        <v>-63.636363636363</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="M18" s="15">
         <v>-69.230769230769</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.992481203007</v>
+        <v>-97.202797202797</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="F19" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G19" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H19" s="15">
-        <v>-40</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I19" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J19" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K19" s="15">
-        <v>-20.833333333333</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="L19" s="15">
-        <v>-44.117647058823</v>
+        <v>-40.540540540540</v>
       </c>
       <c r="M19" s="15">
-        <v>-24</v>
+        <v>-12</v>
       </c>
       <c r="N19" s="15">
-        <v>-36.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1103,11 +1103,11 @@
       <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
       </c>
       <c r="F20" s="14">
         <v>3</v>
@@ -1119,22 +1119,22 @@
         <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K20" s="15">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L20" s="15">
-        <v>-55.555555555555</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="M20" s="15">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.5</v>
+        <v>-88.157894736842</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D21" s="17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E21" s="18">
         <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G21" s="17">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H21" s="18">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I21" s="17">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="J21" s="17">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="K21" s="18">
-        <v>8.064516129032</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L21" s="18">
-        <v>-41.739130434782</v>
+        <v>-41.860465116279</v>
       </c>
       <c r="M21" s="18">
-        <v>-11.842105263157</v>
+        <v>-2.597402597402</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.747126436781</v>
+        <v>-80.211081794195</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1185,20 +1185,20 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="14">
-        <v>1</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>2</v>
@@ -1226,29 +1226,29 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
         <v>1</v>
       </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
+      <c r="G23" s="14">
+        <v>1</v>
+      </c>
+      <c r="H23" s="15">
+        <v>0</v>
       </c>
       <c r="I23" s="14">
         <v>2</v>
       </c>
       <c r="J23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="L23" s="15">
         <v>-80</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D24" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E24" s="15">
-        <v>33.333333333333</v>
+        <v>20</v>
       </c>
       <c r="F24" s="14">
         <v>37</v>
       </c>
       <c r="G24" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H24" s="15">
-        <v>15.625</v>
+        <v>12.121212121212</v>
       </c>
       <c r="I24" s="14">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="J24" s="14">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="K24" s="15">
-        <v>15.217391304347</v>
+        <v>15.463917525773</v>
       </c>
       <c r="L24" s="15">
-        <v>-0.934579439252</v>
+        <v>-1.754385964912</v>
       </c>
       <c r="M24" s="15">
-        <v>65.625</v>
+        <v>67.164179104477</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>-14.285714285714</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="14">
         <v>13</v>
       </c>
       <c r="G25" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H25" s="15">
-        <v>-27.777777777777</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="I25" s="14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J25" s="14">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K25" s="15">
-        <v>-4.081632653061</v>
+        <v>-5.769230769230</v>
       </c>
       <c r="L25" s="15">
-        <v>9.302325581395</v>
+        <v>6.521739130434</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1346,38 +1346,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="14">
-        <v>2</v>
+      <c r="C26" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D26" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F26" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G26" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H26" s="15">
-        <v>23.076923076923</v>
+        <v>44.444444444444</v>
       </c>
       <c r="I26" s="14">
         <v>34</v>
       </c>
       <c r="J26" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K26" s="15">
-        <v>-12.820512820512</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="L26" s="15">
-        <v>-34.615384615384</v>
+        <v>-40.350877192982</v>
       </c>
       <c r="M26" s="15">
-        <v>-50</v>
+        <v>-52.777777777777</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1428,8 +1428,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>2</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1438,25 +1438,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J28" s="14">
         <v>4</v>
       </c>
       <c r="K28" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,8 +1469,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1479,7 +1479,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1488,7 +1488,7 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1497,21 +1497,21 @@
         <v>21</v>
       </c>
       <c r="L29" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1520,7 +1520,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1529,7 +1529,7 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1538,13 +1538,13 @@
         <v>21</v>
       </c>
       <c r="L30" s="15">
+        <v>0</v>
+      </c>
+      <c r="M30" s="15">
+        <v>0</v>
+      </c>
+      <c r="N30" s="15">
         <v>-50</v>
-      </c>
-      <c r="M30" s="15">
-        <v>-50</v>
-      </c>
-      <c r="N30" s="15">
-        <v>-75</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-100pct.xlsx
+++ b/data/source/weekly/cs-en-us-100pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -698,7 +698,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -936,41 +936,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>2</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
         <v>2</v>
       </c>
       <c r="G16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I16" s="14">
         <v>11</v>
       </c>
       <c r="J16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K16" s="15">
-        <v>37.5</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L16" s="15">
-        <v>-8.333333333333</v>
+        <v>-31.25</v>
       </c>
       <c r="M16" s="15">
         <v>-15.384615384615</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.258064516129</v>
+        <v>-83.582089552238</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>400</v>
       </c>
       <c r="F17" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G17" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H17" s="15">
-        <v>366.666666666667</v>
+        <v>275</v>
       </c>
       <c r="I17" s="14">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J17" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K17" s="15">
-        <v>64.705882352941</v>
+        <v>83.333333333333</v>
       </c>
       <c r="L17" s="15">
-        <v>-40.425531914893</v>
+        <v>-31.25</v>
       </c>
       <c r="M17" s="15">
-        <v>55.555555555555</v>
+        <v>83.333333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>-50.877192982456</v>
+        <v>-44.067796610169</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1021,38 +1021,38 @@
       <c r="C18" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
         <v>1</v>
       </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H18" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J18" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K18" s="15">
-        <v>-60</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="L18" s="15">
-        <v>-69.230769230769</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="M18" s="15">
-        <v>-69.230769230769</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="N18" s="15">
-        <v>-97.202797202797</v>
+        <v>-96.644295302013</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,81 +1060,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E19" s="15">
-        <v>-25</v>
+        <v>100</v>
       </c>
       <c r="F19" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G19" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H19" s="15">
-        <v>-41.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J19" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K19" s="15">
-        <v>-21.428571428571</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="L19" s="15">
-        <v>-40.540540540540</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M19" s="15">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="N19" s="15">
-        <v>-33.333333333333</v>
+        <v>-27.777777777777</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>0</v>
-      </c>
-      <c r="F20" s="14">
-        <v>3</v>
-      </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J20" s="14">
         <v>6</v>
       </c>
       <c r="K20" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-52.631578947368</v>
+        <v>-61.904761904761</v>
       </c>
       <c r="M20" s="15">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.157894736842</v>
+        <v>-90.804597701149</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,48 +1142,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" s="17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F21" s="17">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G21" s="17">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H21" s="18">
-        <v>8</v>
+        <v>31.818181818181</v>
       </c>
       <c r="I21" s="17">
+        <v>84</v>
+      </c>
+      <c r="J21" s="17">
         <v>75</v>
       </c>
-      <c r="J21" s="17">
-        <v>70</v>
-      </c>
       <c r="K21" s="18">
-        <v>7.142857142857</v>
+        <v>12</v>
       </c>
       <c r="L21" s="18">
-        <v>-41.860465116279</v>
+        <v>-40</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.597402597402</v>
+        <v>6.329113924050</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.211081794195</v>
+        <v>-79.310344827586</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>2</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1191,29 +1191,29 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="F22" s="14">
+        <v>2</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="I22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J22" s="14">
         <v>1</v>
       </c>
       <c r="K22" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L22" s="15">
-        <v>-60</v>
+        <v>-20</v>
       </c>
       <c r="M22" s="15">
-        <v>-60</v>
+        <v>-20</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,38 +1223,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="C23" s="14">
+        <v>2</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G23" s="14">
         <v>1</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J23" s="14">
         <v>4</v>
       </c>
       <c r="K23" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="M23" s="15">
-        <v>-77.777777777777</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E24" s="15">
-        <v>20</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F24" s="14">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G24" s="14">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H24" s="15">
-        <v>12.121212121212</v>
+        <v>3.333333333333</v>
       </c>
       <c r="I24" s="14">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="J24" s="14">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="K24" s="15">
-        <v>15.463917525773</v>
+        <v>11.538461538461</v>
       </c>
       <c r="L24" s="15">
-        <v>-1.754385964912</v>
+        <v>-4.918032786885</v>
       </c>
       <c r="M24" s="15">
-        <v>67.164179104477</v>
+        <v>56.756756756756</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>-33.333333333333</v>
+        <v>-80</v>
       </c>
       <c r="F25" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G25" s="14">
         <v>21</v>
       </c>
       <c r="H25" s="15">
-        <v>-38.095238095238</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="I25" s="14">
         <v>49</v>
       </c>
       <c r="J25" s="14">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K25" s="15">
-        <v>-5.769230769230</v>
+        <v>-14.035087719298</v>
       </c>
       <c r="L25" s="15">
-        <v>6.521739130434</v>
+        <v>-9.259259259259</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1346,38 +1346,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>20</v>
+      <c r="C26" s="14">
+        <v>3</v>
       </c>
       <c r="D26" s="14">
         <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G26" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H26" s="15">
-        <v>44.444444444444</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J26" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K26" s="15">
-        <v>-19.047619047619</v>
+        <v>-17.777777777777</v>
       </c>
       <c r="L26" s="15">
-        <v>-40.350877192982</v>
+        <v>-40.322580645161</v>
       </c>
       <c r="M26" s="15">
-        <v>-52.777777777777</v>
+        <v>-51.948051948051</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
         <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K28" s="15">
         <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,17 +1469,17 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="14">
         <v>1</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="14">
-        <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1510,17 +1510,17 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="14">
         <v>1</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="14">
-        <v>2</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-100pct.xlsx
+++ b/data/source/weekly/cs-en-us-100pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -940,7 +940,7 @@
         <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
         <v>-100</v>
@@ -949,28 +949,28 @@
         <v>2</v>
       </c>
       <c r="G16" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>-50</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I16" s="14">
         <v>11</v>
       </c>
       <c r="J16" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K16" s="15">
-        <v>22.222222222222</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="L16" s="15">
         <v>-31.25</v>
       </c>
       <c r="M16" s="15">
-        <v>-15.384615384615</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.582089552238</v>
+        <v>-85.526315789473</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G17" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H17" s="15">
-        <v>275</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J17" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K17" s="15">
-        <v>83.333333333333</v>
+        <v>80</v>
       </c>
       <c r="L17" s="15">
-        <v>-31.25</v>
+        <v>-26.530612244898</v>
       </c>
       <c r="M17" s="15">
-        <v>83.333333333333</v>
+        <v>80</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.067796610169</v>
+        <v>-42.857142857142</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1031,19 +1031,19 @@
         <v>1</v>
       </c>
       <c r="G18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I18" s="14">
         <v>5</v>
       </c>
       <c r="J18" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K18" s="15">
-        <v>-54.545454545454</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="L18" s="15">
         <v>-64.285714285714</v>
@@ -1052,7 +1052,7 @@
         <v>-61.538461538461</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.644295302013</v>
+        <v>-96.774193548387</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D19" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G19" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H19" s="15">
         <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J19" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K19" s="15">
-        <v>-13.333333333333</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="L19" s="15">
-        <v>-33.333333333333</v>
+        <v>-34.146341463414</v>
       </c>
       <c r="M19" s="15">
-        <v>0</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="N19" s="15">
-        <v>-27.777777777777</v>
+        <v>-27.027027027027</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1113,10 +1113,10 @@
         <v>1</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
         <v>8</v>
@@ -1134,7 +1134,7 @@
         <v>60</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.804597701149</v>
+        <v>-92</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,48 +1142,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D21" s="17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E21" s="18">
-        <v>80</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F21" s="17">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G21" s="17">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H21" s="18">
-        <v>31.818181818181</v>
+        <v>3.846153846153</v>
       </c>
       <c r="I21" s="17">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J21" s="17">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="K21" s="18">
-        <v>12</v>
+        <v>7.317073170731</v>
       </c>
       <c r="L21" s="18">
-        <v>-40</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M21" s="18">
-        <v>6.329113924050</v>
+        <v>2.325581395348</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.310344827586</v>
+        <v>-79.954441913439</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>2</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1210,7 +1210,7 @@
         <v>300</v>
       </c>
       <c r="L22" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M22" s="15">
         <v>-20</v>
@@ -1223,23 +1223,23 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="14">
         <v>2</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="14">
-        <v>3</v>
       </c>
       <c r="G23" s="14">
         <v>1</v>
       </c>
       <c r="H23" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I23" s="14">
         <v>4</v>
@@ -1254,7 +1254,7 @@
         <v>-60</v>
       </c>
       <c r="M23" s="15">
-        <v>-55.555555555555</v>
+        <v>-60</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D24" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E24" s="15">
-        <v>-28.571428571428</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F24" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G24" s="14">
         <v>30</v>
       </c>
       <c r="H24" s="15">
-        <v>3.333333333333</v>
+        <v>10</v>
       </c>
       <c r="I24" s="14">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="J24" s="14">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="K24" s="15">
-        <v>11.538461538461</v>
+        <v>12.389380530973</v>
       </c>
       <c r="L24" s="15">
-        <v>-4.918032786885</v>
+        <v>0.793650793650</v>
       </c>
       <c r="M24" s="15">
-        <v>56.756756756756</v>
+        <v>69.333333333333</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
-        <v>-80</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G25" s="14">
         <v>21</v>
       </c>
       <c r="H25" s="15">
-        <v>-47.619047619047</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I25" s="14">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="J25" s="14">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="K25" s="15">
-        <v>-14.035087719298</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L25" s="15">
-        <v>-9.259259259259</v>
+        <v>0</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D26" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="14">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G26" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H26" s="15">
-        <v>-8.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I26" s="14">
         <v>37</v>
       </c>
       <c r="J26" s="14">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K26" s="15">
-        <v>-17.777777777777</v>
+        <v>-21.276595744680</v>
       </c>
       <c r="L26" s="15">
-        <v>-40.322580645161</v>
+        <v>-47.887323943662</v>
       </c>
       <c r="M26" s="15">
-        <v>-51.948051948051</v>
+        <v>-58.426966292134</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1396,8 +1396,8 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="F27" s="14">
+        <v>1</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1405,17 +1405,17 @@
       <c r="H27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I27" s="13" t="s">
-        <v>20</v>
+      <c r="I27" s="14">
+        <v>1</v>
       </c>
       <c r="J27" s="14">
         <v>1</v>
       </c>
       <c r="K27" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,14 +1428,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>3</v>
@@ -1450,13 +1450,13 @@
         <v>5</v>
       </c>
       <c r="J28" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L28" s="15">
-        <v>-16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-100pct.xlsx
+++ b/data/source/weekly/cs-en-us-100pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -698,7 +698,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -940,7 +940,7 @@
         <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
         <v>-100</v>
@@ -949,19 +949,19 @@
         <v>2</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>-71.428571428571</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I16" s="14">
         <v>11</v>
       </c>
       <c r="J16" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K16" s="15">
-        <v>-8.333333333333</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="L16" s="15">
         <v>-31.25</v>
@@ -970,89 +970,89 @@
         <v>-26.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.526315789473</v>
+        <v>-86.746987951807</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="14">
-        <v>3</v>
+      <c r="C17" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="F17" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G17" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H17" s="15">
-        <v>133.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
         <v>36</v>
       </c>
       <c r="J17" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K17" s="15">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L17" s="15">
         <v>-26.530612244898</v>
       </c>
       <c r="M17" s="15">
-        <v>80</v>
+        <v>63.636363636363</v>
       </c>
       <c r="N17" s="15">
-        <v>-42.857142857142</v>
+        <v>-43.75</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
         <v>1</v>
       </c>
       <c r="G18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="I18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J18" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K18" s="15">
-        <v>-58.333333333333</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L18" s="15">
-        <v>-64.285714285714</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M18" s="15">
-        <v>-61.538461538461</v>
+        <v>-60</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.774193548387</v>
+        <v>-96.296296296296</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
+        <v>-60</v>
+      </c>
+      <c r="F19" s="14">
+        <v>10</v>
+      </c>
+      <c r="G19" s="14">
+        <v>12</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-16.666666666666</v>
+      </c>
+      <c r="I19" s="14">
+        <v>29</v>
+      </c>
+      <c r="J19" s="14">
+        <v>36</v>
+      </c>
+      <c r="K19" s="15">
+        <v>-19.444444444444</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-36.956521739130</v>
+      </c>
+      <c r="M19" s="15">
         <v>0</v>
       </c>
-      <c r="F19" s="14">
-        <v>9</v>
-      </c>
-      <c r="G19" s="14">
-        <v>9</v>
-      </c>
-      <c r="H19" s="15">
-        <v>0</v>
-      </c>
-      <c r="I19" s="14">
-        <v>27</v>
-      </c>
-      <c r="J19" s="14">
-        <v>31</v>
-      </c>
-      <c r="K19" s="15">
-        <v>-12.903225806451</v>
-      </c>
-      <c r="L19" s="15">
-        <v>-34.146341463414</v>
-      </c>
-      <c r="M19" s="15">
-        <v>-6.896551724137</v>
-      </c>
       <c r="N19" s="15">
-        <v>-27.027027027027</v>
+        <v>-30.952380952381</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1109,14 +1109,14 @@
       <c r="E20" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="14">
-        <v>1</v>
+      <c r="F20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G20" s="14">
         <v>1</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="14">
         <v>8</v>
@@ -1134,7 +1134,7 @@
         <v>60</v>
       </c>
       <c r="N20" s="15">
-        <v>-92</v>
+        <v>-92.857142857142</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D21" s="17">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>-42.857142857142</v>
+        <v>-76.923076923076</v>
       </c>
       <c r="F21" s="17">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G21" s="17">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H21" s="18">
-        <v>3.846153846153</v>
+        <v>-30.303030303030</v>
       </c>
       <c r="I21" s="17">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J21" s="17">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K21" s="18">
-        <v>7.317073170731</v>
+        <v>-4.210526315789</v>
       </c>
       <c r="L21" s="18">
-        <v>-38.461538461538</v>
+        <v>-38.513513513513</v>
       </c>
       <c r="M21" s="18">
-        <v>2.325581395348</v>
+        <v>1.111111111111</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.954441913439</v>
+        <v>-80.679405520169</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1194,11 +1194,11 @@
       <c r="F22" s="14">
         <v>2</v>
       </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>100</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>4</v>
@@ -1210,7 +1210,7 @@
         <v>300</v>
       </c>
       <c r="L22" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M22" s="15">
         <v>-20</v>
@@ -1223,38 +1223,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="C23" s="14">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>0</v>
       </c>
       <c r="F23" s="14">
+        <v>3</v>
+      </c>
+      <c r="G23" s="14">
         <v>2</v>
       </c>
-      <c r="G23" s="14">
-        <v>1</v>
-      </c>
       <c r="H23" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K23" s="15">
         <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="M23" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E24" s="15">
-        <v>11.111111111111</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="F24" s="14">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G24" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H24" s="15">
-        <v>10</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="I24" s="14">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="J24" s="14">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="K24" s="15">
-        <v>12.389380530973</v>
+        <v>7.936507936507</v>
       </c>
       <c r="L24" s="15">
-        <v>0.793650793650</v>
+        <v>3.816793893129</v>
       </c>
       <c r="M24" s="15">
-        <v>69.333333333333</v>
+        <v>74.358974358974</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>16.666666666666</v>
+        <v>-60</v>
       </c>
       <c r="F25" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G25" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H25" s="15">
-        <v>-28.571428571428</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="I25" s="14">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J25" s="14">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="K25" s="15">
-        <v>-11.111111111111</v>
+        <v>-14.705882352941</v>
       </c>
       <c r="L25" s="15">
-        <v>0</v>
+        <v>1.754385964912</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G26" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H26" s="15">
-        <v>-50</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="I26" s="14">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J26" s="14">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K26" s="15">
-        <v>-21.276595744680</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="L26" s="15">
-        <v>-47.887323943662</v>
+        <v>-42.465753424657</v>
       </c>
       <c r="M26" s="15">
-        <v>-58.426966292134</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
         <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" s="14">
         <v>7</v>
       </c>
       <c r="K28" s="15">
-        <v>-28.571428571428</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L28" s="15">
-        <v>-28.571428571428</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-100pct.xlsx
+++ b/data/source/weekly/cs-en-us-100pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -939,20 +939,20 @@
       <c r="C16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="14">
-        <v>2</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F16" s="14">
-        <v>2</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G16" s="14">
         <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I16" s="14">
         <v>11</v>
@@ -964,95 +964,95 @@
         <v>-21.428571428571</v>
       </c>
       <c r="L16" s="15">
+        <v>-35.294117647058</v>
+      </c>
+      <c r="M16" s="15">
         <v>-31.25</v>
       </c>
-      <c r="M16" s="15">
-        <v>-26.666666666666</v>
-      </c>
       <c r="N16" s="15">
-        <v>-86.746987951807</v>
+        <v>-87.209302325581</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
+      <c r="C17" s="14">
+        <v>1</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G17" s="14">
         <v>10</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="I17" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J17" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K17" s="15">
-        <v>50</v>
+        <v>37.037037037037</v>
       </c>
       <c r="L17" s="15">
-        <v>-26.530612244898</v>
+        <v>-26</v>
       </c>
       <c r="M17" s="15">
-        <v>63.636363636363</v>
+        <v>60.869565217391</v>
       </c>
       <c r="N17" s="15">
-        <v>-43.75</v>
+        <v>-47.142857142857</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
         <v>1</v>
       </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>-75</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="I18" s="14">
         <v>6</v>
       </c>
       <c r="J18" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K18" s="15">
-        <v>-57.142857142857</v>
+        <v>-64.705882352941</v>
       </c>
       <c r="L18" s="15">
-        <v>-57.142857142857</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M18" s="15">
-        <v>-60</v>
+        <v>-62.5</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.296296296296</v>
+        <v>-96.385542168674</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>3</v>
+      </c>
+      <c r="D19" s="14">
         <v>2</v>
       </c>
-      <c r="D19" s="14">
-        <v>5</v>
-      </c>
       <c r="E19" s="15">
-        <v>-60</v>
+        <v>50</v>
       </c>
       <c r="F19" s="14">
         <v>10</v>
       </c>
       <c r="G19" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H19" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J19" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K19" s="15">
-        <v>-19.444444444444</v>
+        <v>-13.157894736842</v>
       </c>
       <c r="L19" s="15">
-        <v>-36.956521739130</v>
+        <v>-31.25</v>
       </c>
       <c r="M19" s="15">
-        <v>0</v>
+        <v>6.451612903225</v>
       </c>
       <c r="N19" s="15">
-        <v>-30.952380952381</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1103,11 +1103,11 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="13" t="s">
         <v>20</v>
@@ -1122,19 +1122,19 @@
         <v>8</v>
       </c>
       <c r="J20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K20" s="15">
-        <v>33.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L20" s="15">
-        <v>-61.904761904761</v>
+        <v>-65.217391304347</v>
       </c>
       <c r="M20" s="15">
         <v>60</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.857142857142</v>
+        <v>-93.495934959349</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E21" s="18">
-        <v>-76.923076923076</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F21" s="17">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G21" s="17">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H21" s="18">
-        <v>-30.303030303030</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="I21" s="17">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="J21" s="17">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.210526315789</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L21" s="18">
-        <v>-38.513513513513</v>
+        <v>-39.240506329113</v>
       </c>
       <c r="M21" s="18">
-        <v>1.111111111111</v>
+        <v>1.052631578947</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.679405520169</v>
+        <v>-80.722891566265</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1223,14 +1223,14 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
         <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
         <v>3</v>
@@ -1245,13 +1245,13 @@
         <v>5</v>
       </c>
       <c r="J23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L23" s="15">
-        <v>-50</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="M23" s="15">
         <v>-50</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D24" s="14">
         <v>13</v>
       </c>
       <c r="E24" s="15">
-        <v>-30.769230769230</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="F24" s="14">
         <v>31</v>
       </c>
       <c r="G24" s="14">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H24" s="15">
-        <v>-8.823529411764</v>
+        <v>-26.190476190476</v>
       </c>
       <c r="I24" s="14">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="J24" s="14">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="K24" s="15">
-        <v>7.936507936507</v>
+        <v>2.158273381294</v>
       </c>
       <c r="L24" s="15">
-        <v>3.816793893129</v>
+        <v>2.158273381294</v>
       </c>
       <c r="M24" s="15">
-        <v>74.358974358974</v>
+        <v>75.308641975308</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
         <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="F25" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G25" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H25" s="15">
-        <v>-36.842105263157</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="I25" s="14">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J25" s="14">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K25" s="15">
-        <v>-14.705882352941</v>
+        <v>-16.438356164383</v>
       </c>
       <c r="L25" s="15">
-        <v>1.754385964912</v>
+        <v>-3.174603174603</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
         <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G26" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H26" s="15">
-        <v>-38.461538461538</v>
+        <v>-12.5</v>
       </c>
       <c r="I26" s="14">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J26" s="14">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="K26" s="15">
-        <v>-19.230769230769</v>
+        <v>-17.241379310344</v>
       </c>
       <c r="L26" s="15">
-        <v>-42.465753424657</v>
+        <v>-37.662337662337</v>
       </c>
       <c r="M26" s="15">
-        <v>-57.142857142857</v>
+        <v>-54.285714285714</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1428,8 +1428,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
         <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>33.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
         <v>6</v>
@@ -1478,8 +1478,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1519,8 +1519,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-100pct.xlsx
+++ b/data/source/weekly/cs-en-us-100pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -939,11 +939,11 @@
       <c r="C16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="D16" s="14">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-100</v>
       </c>
       <c r="F16" s="13" t="s">
         <v>20</v>
@@ -958,19 +958,19 @@
         <v>11</v>
       </c>
       <c r="J16" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K16" s="15">
-        <v>-21.428571428571</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="L16" s="15">
         <v>-35.294117647058</v>
       </c>
       <c r="M16" s="15">
-        <v>-31.25</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.209302325581</v>
+        <v>-87.912087912087</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
         <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G17" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H17" s="15">
-        <v>-10</v>
+        <v>-50</v>
       </c>
       <c r="I17" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J17" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K17" s="15">
-        <v>37.037037037037</v>
+        <v>30</v>
       </c>
       <c r="L17" s="15">
-        <v>-26</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="M17" s="15">
-        <v>60.869565217391</v>
+        <v>39.285714285714</v>
       </c>
       <c r="N17" s="15">
-        <v>-47.142857142857</v>
+        <v>-45.833333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>2</v>
       </c>
       <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>100</v>
+      </c>
+      <c r="F18" s="14">
         <v>3</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F18" s="14">
-        <v>1</v>
       </c>
       <c r="G18" s="14">
         <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>-85.714285714285</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I18" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J18" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K18" s="15">
-        <v>-64.705882352941</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L18" s="15">
-        <v>-66.666666666666</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="M18" s="15">
-        <v>-62.5</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.385542168674</v>
+        <v>-95.580110497237</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" s="14">
         <v>2</v>
       </c>
       <c r="E19" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G19" s="14">
         <v>10</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="I19" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J19" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K19" s="15">
-        <v>-13.157894736842</v>
+        <v>-12.5</v>
       </c>
       <c r="L19" s="15">
-        <v>-31.25</v>
+        <v>-27.083333333333</v>
       </c>
       <c r="M19" s="15">
-        <v>6.451612903225</v>
+        <v>6.060606060606</v>
       </c>
       <c r="N19" s="15">
-        <v>-25</v>
+        <v>-27.083333333333</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1103,11 +1103,11 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="13" t="s">
         <v>20</v>
@@ -1128,13 +1128,13 @@
         <v>14.285714285714</v>
       </c>
       <c r="L20" s="15">
-        <v>-65.217391304347</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M20" s="15">
         <v>60</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.495934959349</v>
+        <v>-93.650793650793</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D21" s="17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E21" s="18">
-        <v>-55.555555555555</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F21" s="17">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G21" s="17">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H21" s="18">
-        <v>-41.176470588235</v>
+        <v>-52.777777777777</v>
       </c>
       <c r="I21" s="17">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="J21" s="17">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.692307692307</v>
+        <v>-8.108108108108</v>
       </c>
       <c r="L21" s="18">
-        <v>-39.240506329113</v>
+        <v>-38.922155688622</v>
       </c>
       <c r="M21" s="18">
-        <v>1.052631578947</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.722891566265</v>
+        <v>-80.645161290322</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,8 +1191,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="14">
-        <v>2</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1213,7 +1213,7 @@
         <v>-42.857142857142</v>
       </c>
       <c r="M22" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1227,34 +1227,34 @@
         <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
         <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G23" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>50</v>
+        <v>-80</v>
       </c>
       <c r="I23" s="14">
         <v>5</v>
       </c>
       <c r="J23" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K23" s="15">
-        <v>-16.666666666666</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L23" s="15">
         <v>-54.545454545454</v>
       </c>
       <c r="M23" s="15">
-        <v>-50</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D24" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E24" s="15">
-        <v>-46.153846153846</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="F24" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G24" s="14">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H24" s="15">
-        <v>-26.190476190476</v>
+        <v>-26.530612244898</v>
       </c>
       <c r="I24" s="14">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="J24" s="14">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="K24" s="15">
-        <v>2.158273381294</v>
+        <v>0</v>
       </c>
       <c r="L24" s="15">
-        <v>2.158273381294</v>
+        <v>6.25</v>
       </c>
       <c r="M24" s="15">
-        <v>75.308641975308</v>
+        <v>80</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G25" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H25" s="15">
-        <v>-38.095238095238</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I25" s="14">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="J25" s="14">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="K25" s="15">
-        <v>-16.438356164383</v>
+        <v>-15.189873417721</v>
       </c>
       <c r="L25" s="15">
-        <v>-3.174603174603</v>
+        <v>1.515151515151</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E26" s="15">
+        <v>25</v>
+      </c>
+      <c r="F26" s="14">
+        <v>17</v>
+      </c>
+      <c r="G26" s="14">
+        <v>17</v>
+      </c>
+      <c r="H26" s="15">
         <v>0</v>
       </c>
-      <c r="F26" s="14">
-        <v>14</v>
-      </c>
-      <c r="G26" s="14">
-        <v>16</v>
-      </c>
-      <c r="H26" s="15">
-        <v>-12.5</v>
-      </c>
       <c r="I26" s="14">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J26" s="14">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K26" s="15">
-        <v>-17.241379310344</v>
+        <v>-14.516129032258</v>
       </c>
       <c r="L26" s="15">
-        <v>-37.662337662337</v>
+        <v>-36.904761904761</v>
       </c>
       <c r="M26" s="15">
-        <v>-54.285714285714</v>
+        <v>-53.913043478260</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1428,8 +1428,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1441,22 +1441,22 @@
         <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J28" s="14">
         <v>7</v>
       </c>
       <c r="K28" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>-14.285714285714</v>
+        <v>-12.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,10 +1497,10 @@
         <v>21</v>
       </c>
       <c r="L29" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N29" s="15">
         <v>-60</v>
@@ -1538,10 +1538,10 @@
         <v>21</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M30" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N30" s="15">
         <v>-50</v>
